--- a/Contingencia_Respaldo_360__BP.xlsx
+++ b/Contingencia_Respaldo_360__BP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aseguroca-my.sharepoint.com/personal/hchavarria_grupoasys_com/Documents/Documentos/Documentos/B Popular/Cotización Autoexpedible/Respaldo 360/Kit de Bienvenida/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ricardo.blanco\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{744D24AF-4E1B-41C7-88B9-524C47748E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1E74F26-2F6C-400E-8FB9-3020A2162774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificado" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_GoBack" localSheetId="0">Certificado!#REF!</definedName>
     <definedName name="_GoBack" localSheetId="1">'desempleo 1'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Certificado!$A$1:$P$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Certificado!$B$2:$O$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'desempleo 1'!$C$2:$O$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="139">
   <si>
     <t>DATOS DE LAS PÓLIZAS</t>
   </si>
@@ -449,9 +449,6 @@
     <t xml:space="preserve">Estado Civil: </t>
   </si>
   <si>
-    <t>UM</t>
-  </si>
-  <si>
     <t>Correo Electrónico:</t>
   </si>
   <si>
@@ -626,9 +623,6 @@
   </si>
   <si>
     <t xml:space="preserve">INDICACIÓN DE LA ENTREGA DE LA INFORMACIÓN PREVIO AL PERFECCIONAMIENTO DEL CONTRATO </t>
-  </si>
-  <si>
-    <t>Incluido / No Incluido</t>
   </si>
   <si>
     <t>SEGURO COLECTIVO RESPALDO 360</t>
@@ -772,6 +766,9 @@
   </si>
   <si>
     <t>La documentación contractual y la nota técnica que integran este producto, están registrados ante la Superintendencia General de Seguros de conformidad con lo dispuesto por el artículo 29, inciso d) de la Ley Reguladora del Mercado de Seguros No. 8653, bajo el registro G07-46-A0-1133, de fecha 13 de junio  del 2025.</t>
+  </si>
+  <si>
+    <t>Incluido</t>
   </si>
 </sst>
 </file>
@@ -2057,6 +2054,249 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2075,24 +2315,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2120,24 +2342,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2165,218 +2369,86 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2426,12 +2498,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2486,80 +2552,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -2614,7 +2611,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2622,7 +2619,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2634,7 +2631,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2642,7 +2639,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2662,14 +2659,6 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2705,140 +2694,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="absolute">
-        <xdr:from>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>7</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9227" name="Check Box 11" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s9227"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B240000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData fLocksWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="absolute">
-        <xdr:from>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>114300</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>76200</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9228" name="Check Box 12" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s9228"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C240000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData fLocksWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>3</xdr:col>
@@ -2848,9 +2703,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>12700</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2917,7 +2772,7 @@
           <xdr:col>8</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>12700</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2976,13 +2831,13 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>101600</xdr:colOff>
+          <xdr:colOff>99060</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>406400</xdr:colOff>
+          <xdr:colOff>403860</xdr:colOff>
           <xdr:row>36</xdr:row>
           <xdr:rowOff>190500</xdr:rowOff>
         </xdr:to>
@@ -3043,15 +2898,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>88900</xdr:colOff>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>101600</xdr:colOff>
+          <xdr:colOff>99060</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3110,15 +2965,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>25400</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>9</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>12700</xdr:rowOff>
+          <xdr:rowOff>15240</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3179,13 +3034,13 @@
           <xdr:col>12</xdr:col>
           <xdr:colOff>114300</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>444500</xdr:colOff>
+          <xdr:colOff>441960</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3244,13 +3099,13 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>203200</xdr:colOff>
+          <xdr:colOff>205740</xdr:colOff>
           <xdr:row>41</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>7</xdr:col>
-          <xdr:colOff>127000</xdr:colOff>
+          <xdr:colOff>129540</xdr:colOff>
           <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -3313,11 +3168,11 @@
           <xdr:col>11</xdr:col>
           <xdr:colOff>495300</xdr:colOff>
           <xdr:row>41</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>175260</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>63500</xdr:colOff>
+          <xdr:colOff>60960</xdr:colOff>
           <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -3378,7 +3233,7 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>444500</xdr:colOff>
+          <xdr:colOff>441960</xdr:colOff>
           <xdr:row>33</xdr:row>
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:from>
@@ -3386,7 +3241,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>304800</xdr:colOff>
           <xdr:row>37</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3445,15 +3300,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>7</xdr:col>
-          <xdr:colOff>165100</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>19</xdr:row>
-          <xdr:rowOff>127000</xdr:rowOff>
+          <xdr:rowOff>129540</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>7</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>632460</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>22860</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3512,15 +3367,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>19</xdr:row>
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>632460</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>50800</xdr:rowOff>
+          <xdr:rowOff>53340</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3582,8 +3437,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1054537</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3526</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>2721</xdr:rowOff>
     </xdr:to>
@@ -3718,13 +3573,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>165100</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>281940</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>469900</xdr:colOff>
+          <xdr:colOff>472440</xdr:colOff>
           <xdr:row>31</xdr:row>
           <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
@@ -3785,15 +3640,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>165100</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>30</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>469900</xdr:colOff>
+          <xdr:colOff>472440</xdr:colOff>
           <xdr:row>32</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3852,15 +3707,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>31</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>482600</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3919,15 +3774,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>32</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>482600</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>34</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3994,7 +3849,7 @@
           <xdr:col>14</xdr:col>
           <xdr:colOff>495300</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4053,13 +3908,13 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>165100</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>281940</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>469900</xdr:colOff>
+          <xdr:colOff>472440</xdr:colOff>
           <xdr:row>23</xdr:row>
           <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
@@ -4120,15 +3975,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>165100</xdr:colOff>
+          <xdr:colOff>167640</xdr:colOff>
           <xdr:row>22</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>469900</xdr:colOff>
+          <xdr:colOff>472440</xdr:colOff>
           <xdr:row>24</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4187,15 +4042,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>23</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>482600</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4254,15 +4109,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>177800</xdr:colOff>
+          <xdr:colOff>175260</xdr:colOff>
           <xdr:row>24</xdr:row>
           <xdr:rowOff>152400</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>14</xdr:col>
-          <xdr:colOff>482600</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4329,7 +4184,7 @@
           <xdr:col>14</xdr:col>
           <xdr:colOff>495300</xdr:colOff>
           <xdr:row>27</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4396,7 +4251,7 @@
           <xdr:col>14</xdr:col>
           <xdr:colOff>495300</xdr:colOff>
           <xdr:row>36</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4463,7 +4318,7 @@
           <xdr:col>14</xdr:col>
           <xdr:colOff>495300</xdr:colOff>
           <xdr:row>28</xdr:row>
-          <xdr:rowOff>63500</xdr:rowOff>
+          <xdr:rowOff>60960</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -4807,164 +4662,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DD9E7C9-8472-470F-A565-68FBC64A2E5E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:P70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6328125" customWidth="1"/>
-    <col min="2" max="2" width="2.1796875" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" style="43" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="6" width="5.36328125" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" customWidth="1"/>
-    <col min="9" max="9" width="2.1796875" customWidth="1"/>
-    <col min="10" max="10" width="3.453125" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="2.21875" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="43" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" customWidth="1"/>
+    <col min="5" max="6" width="5.33203125" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" customWidth="1"/>
+    <col min="9" max="9" width="2.21875" customWidth="1"/>
+    <col min="10" max="10" width="3.44140625" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="14" width="14.1796875" customWidth="1"/>
+    <col min="13" max="14" width="14.21875" customWidth="1"/>
     <col min="15" max="15" width="2" style="18" customWidth="1"/>
-    <col min="16" max="16" width="3.1796875" customWidth="1"/>
-    <col min="17" max="17" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.21875" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:15" s="46" customFormat="1" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:15" s="46" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="47"/>
-      <c r="C2" s="196" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="196"/>
+      <c r="C2" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
       <c r="N2" s="68"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="2:15" s="46" customFormat="1" ht="19.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" s="46" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="50"/>
-      <c r="C3" s="197" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
-      <c r="I3" s="197"/>
-      <c r="J3" s="197"/>
-      <c r="K3" s="197"/>
-      <c r="L3" s="197"/>
-      <c r="M3" s="197"/>
+      <c r="C3" s="98" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
       <c r="N3" s="67"/>
       <c r="O3" s="49"/>
     </row>
-    <row r="4" spans="2:15" s="2" customFormat="1" ht="38.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" s="2" customFormat="1" ht="38.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="51"/>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="160" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="45"/>
+    </row>
+    <row r="5" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="51"/>
+      <c r="C5" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="148"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="148"/>
-      <c r="G4" s="148"/>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="148"/>
-      <c r="L4" s="148"/>
-      <c r="M4" s="148"/>
-      <c r="N4" s="149"/>
-      <c r="O4" s="45"/>
-    </row>
-    <row r="5" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="51"/>
-      <c r="C5" s="103" t="s">
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="45"/>
+    </row>
+    <row r="6" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="51"/>
+      <c r="C6" s="163" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="45"/>
-    </row>
-    <row r="6" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="51"/>
-      <c r="C6" s="150" t="s">
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="164"/>
+      <c r="I6" s="165" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="152"/>
-      <c r="I6" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="151"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
       <c r="N6" s="154"/>
       <c r="O6" s="45"/>
     </row>
-    <row r="7" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="51"/>
-      <c r="C7" s="103" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="105"/>
+      <c r="C7" s="107" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="109"/>
       <c r="O7" s="45"/>
     </row>
-    <row r="8" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="51"/>
       <c r="C8" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="155" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="155"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
-      <c r="I8" s="155"/>
-      <c r="J8" s="155"/>
-      <c r="K8" s="155"/>
-      <c r="L8" s="155"/>
-      <c r="M8" s="155"/>
-      <c r="N8" s="156"/>
+        <v>86</v>
+      </c>
+      <c r="D8" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="166"/>
+      <c r="F8" s="166"/>
+      <c r="G8" s="166"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="166"/>
+      <c r="K8" s="166"/>
+      <c r="L8" s="166"/>
+      <c r="M8" s="166"/>
+      <c r="N8" s="167"/>
       <c r="O8" s="45"/>
     </row>
-    <row r="9" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="51"/>
       <c r="C9" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -4978,35 +4836,35 @@
       <c r="N9" s="72"/>
       <c r="O9" s="45"/>
     </row>
-    <row r="10" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="51"/>
-      <c r="C10" s="103" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="105"/>
+      <c r="C10" s="107" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="109"/>
       <c r="O10" s="45"/>
     </row>
-    <row r="11" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="51"/>
       <c r="C11" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="66"/>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
       <c r="G11" s="66"/>
       <c r="H11" s="84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="65"/>
@@ -5016,48 +4874,48 @@
       <c r="N11" s="86"/>
       <c r="O11" s="45"/>
     </row>
-    <row r="12" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="51"/>
-      <c r="C12" s="103" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="105"/>
+      <c r="C12" s="107" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="109"/>
       <c r="O12" s="45"/>
     </row>
-    <row r="13" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="51"/>
-      <c r="C13" s="161" t="s">
+      <c r="C13" s="172" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="163"/>
-      <c r="K13" s="198" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="199"/>
-      <c r="M13" s="199"/>
-      <c r="N13" s="200"/>
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="174"/>
+      <c r="K13" s="104" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="106"/>
       <c r="O13" s="45"/>
     </row>
-    <row r="14" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="51"/>
       <c r="C14" s="87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="88"/>
       <c r="E14" s="88"/>
@@ -5074,10 +4932,10 @@
       <c r="N14" s="92"/>
       <c r="O14" s="45"/>
     </row>
-    <row r="15" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="51"/>
       <c r="C15" s="93" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" s="94"/>
       <c r="E15" s="94"/>
@@ -5092,28 +4950,28 @@
       <c r="N15" s="96"/>
       <c r="O15" s="45"/>
     </row>
-    <row r="16" spans="2:15" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:15" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="51"/>
-      <c r="C16" s="103" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="105"/>
+      <c r="C16" s="107" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="109"/>
       <c r="O16" s="45"/>
     </row>
-    <row r="17" spans="2:16" s="2" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="51"/>
       <c r="C17" s="73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -5123,17 +4981,17 @@
       <c r="I17" s="1"/>
       <c r="J17" s="75"/>
       <c r="K17" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="74"/>
       <c r="O17" s="45"/>
     </row>
-    <row r="18" spans="2:16" s="2" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="51"/>
       <c r="C18" s="76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -5150,10 +5008,10 @@
       <c r="N18" s="72"/>
       <c r="O18" s="45"/>
     </row>
-    <row r="19" spans="2:16" s="2" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="51"/>
       <c r="C19" s="78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="1"/>
@@ -5170,229 +5028,223 @@
       <c r="N19" s="72"/>
       <c r="O19" s="45"/>
     </row>
-    <row r="20" spans="2:16" s="2" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="51"/>
       <c r="C20" s="80" t="s">
         <v>65</v>
       </c>
       <c r="D20" s="81"/>
-      <c r="E20" s="158" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="159"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="159"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="160"/>
+      <c r="E20" s="169" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="171"/>
       <c r="K20" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L20" s="81"/>
       <c r="M20" s="81"/>
       <c r="N20" s="82"/>
       <c r="O20" s="45"/>
     </row>
-    <row r="21" spans="2:16" s="2" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="51"/>
-      <c r="C21" s="201" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="202"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="202"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="202"/>
-      <c r="K21" s="202"/>
-      <c r="L21" s="202"/>
-      <c r="M21" s="202"/>
-      <c r="N21" s="203"/>
+      <c r="C21" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="112"/>
       <c r="O21" s="45"/>
     </row>
-    <row r="22" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="51"/>
-      <c r="C22" s="103" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="105"/>
+      <c r="C22" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+      <c r="N22" s="109"/>
       <c r="O22" s="45"/>
     </row>
-    <row r="23" spans="2:16" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="51"/>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="113" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="114"/>
+      <c r="E23" s="114"/>
+      <c r="F23" s="114"/>
+      <c r="G23" s="114"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="45"/>
+    </row>
+    <row r="24" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="51"/>
+      <c r="C24" s="107" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+      <c r="N24" s="109"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="51"/>
+      <c r="C25" s="135" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136" t="s">
+        <v>119</v>
+      </c>
+      <c r="N25" s="137"/>
+      <c r="O25" s="45"/>
+    </row>
+    <row r="26" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="59"/>
+      <c r="C26" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="100"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="103"/>
+      <c r="O26" s="45"/>
+    </row>
+    <row r="27" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="59"/>
+      <c r="C27" s="99" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="108"/>
-      <c r="O23" s="45"/>
-    </row>
-    <row r="24" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="51"/>
-      <c r="C24" s="103" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="45"/>
-    </row>
-    <row r="25" spans="2:16" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="51"/>
-      <c r="C25" s="138" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
-      <c r="L25" s="139"/>
-      <c r="M25" s="139" t="s">
-        <v>120</v>
-      </c>
-      <c r="N25" s="140"/>
-      <c r="O25" s="45"/>
-    </row>
-    <row r="26" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="59"/>
-      <c r="C26" s="170" t="s">
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="100"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="103"/>
+      <c r="O27" s="45"/>
+    </row>
+    <row r="28" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="59"/>
+      <c r="C28" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="171"/>
-      <c r="I26" s="171"/>
-      <c r="J26" s="171"/>
-      <c r="K26" s="171"/>
-      <c r="L26" s="172"/>
-      <c r="M26" s="173" t="s">
-        <v>66</v>
-      </c>
-      <c r="N26" s="174"/>
-      <c r="O26" s="45"/>
-    </row>
-    <row r="27" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="59"/>
-      <c r="C27" s="170" t="s">
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="102"/>
+      <c r="N28" s="103"/>
+      <c r="O28" s="45"/>
+    </row>
+    <row r="29" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="59"/>
+      <c r="C29" s="99" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="171"/>
-      <c r="E27" s="171"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="171"/>
-      <c r="I27" s="171"/>
-      <c r="J27" s="171"/>
-      <c r="K27" s="171"/>
-      <c r="L27" s="172"/>
-      <c r="M27" s="173" t="s">
-        <v>66</v>
-      </c>
-      <c r="N27" s="174"/>
-      <c r="O27" s="45"/>
-    </row>
-    <row r="28" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="59"/>
-      <c r="C28" s="170" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="171"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="172"/>
-      <c r="M28" s="173" t="s">
-        <v>66</v>
-      </c>
-      <c r="N28" s="174"/>
-      <c r="O28" s="45"/>
-    </row>
-    <row r="29" spans="2:16" s="2" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="59"/>
-      <c r="C29" s="170" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="171"/>
-      <c r="L29" s="172"/>
-      <c r="M29" s="173" t="s">
-        <v>125</v>
-      </c>
-      <c r="N29" s="174"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="100"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102" t="s">
+        <v>138</v>
+      </c>
+      <c r="N29" s="103"/>
       <c r="O29" s="45"/>
     </row>
-    <row r="30" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="59"/>
-      <c r="C30" s="103" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="105"/>
+      <c r="C30" s="107" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="109"/>
       <c r="O30" s="45"/>
     </row>
-    <row r="31" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="59"/>
       <c r="C31" s="83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" s="66"/>
       <c r="E31" s="66"/>
       <c r="F31" s="66"/>
       <c r="G31" s="66"/>
       <c r="H31" s="84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="65"/>
@@ -5402,654 +5254,652 @@
       <c r="N31" s="86"/>
       <c r="O31" s="45"/>
     </row>
-    <row r="32" spans="2:16" s="52" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="133"/>
-      <c r="C32" s="103" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="105"/>
+    <row r="32" spans="2:16" s="52" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="175"/>
+      <c r="C32" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="109"/>
       <c r="O32" s="53"/>
       <c r="P32" s="60"/>
     </row>
-    <row r="33" spans="2:16" s="52" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="133"/>
-      <c r="C33" s="141" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" s="142"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="142"/>
-      <c r="I33" s="142"/>
-      <c r="J33" s="142"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="142"/>
-      <c r="M33" s="142"/>
-      <c r="N33" s="143"/>
+    <row r="33" spans="2:16" s="52" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="175"/>
+      <c r="C33" s="126" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="127"/>
+      <c r="K33" s="127"/>
+      <c r="L33" s="127"/>
+      <c r="M33" s="127"/>
+      <c r="N33" s="128"/>
       <c r="O33" s="53"/>
       <c r="P33" s="60"/>
     </row>
-    <row r="34" spans="2:16" s="52" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="133"/>
-      <c r="C34" s="134" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-      <c r="M34" s="136" t="s">
-        <v>66</v>
-      </c>
-      <c r="N34" s="137"/>
+    <row r="34" spans="2:16" s="52" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="175"/>
+      <c r="C34" s="263" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="264"/>
+      <c r="E34" s="264"/>
+      <c r="F34" s="264"/>
+      <c r="G34" s="264"/>
+      <c r="H34" s="264"/>
+      <c r="I34" s="264"/>
+      <c r="J34" s="264"/>
+      <c r="K34" s="264"/>
+      <c r="L34" s="264"/>
+      <c r="M34" s="176"/>
+      <c r="N34" s="177"/>
       <c r="O34" s="53"/>
     </row>
-    <row r="35" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="51"/>
-      <c r="C35" s="141" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="142"/>
-      <c r="I35" s="142"/>
-      <c r="J35" s="142"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="142"/>
-      <c r="M35" s="142"/>
-      <c r="N35" s="143"/>
+      <c r="C35" s="126" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
+      <c r="M35" s="127"/>
+      <c r="N35" s="128"/>
       <c r="O35" s="54"/>
       <c r="P35" s="55"/>
     </row>
-    <row r="36" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="51"/>
-      <c r="C36" s="164" t="s">
+      <c r="C36" s="150" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="151"/>
+      <c r="H36" s="151"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="151"/>
+      <c r="K36" s="152" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="165"/>
-      <c r="G36" s="165"/>
-      <c r="H36" s="165"/>
-      <c r="I36" s="165"/>
-      <c r="J36" s="165"/>
-      <c r="K36" s="166" t="s">
-        <v>101</v>
-      </c>
-      <c r="L36" s="151"/>
-      <c r="M36" s="151"/>
+      <c r="L36" s="153"/>
+      <c r="M36" s="153"/>
       <c r="N36" s="154"/>
       <c r="O36" s="54"/>
       <c r="P36" s="55"/>
     </row>
-    <row r="37" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="51"/>
-      <c r="C37" s="167" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
-      <c r="M37" s="168"/>
-      <c r="N37" s="169"/>
+      <c r="C37" s="155" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="156"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="156"/>
+      <c r="G37" s="156"/>
+      <c r="H37" s="156"/>
+      <c r="I37" s="156"/>
+      <c r="J37" s="156"/>
+      <c r="K37" s="156"/>
+      <c r="L37" s="156"/>
+      <c r="M37" s="156"/>
+      <c r="N37" s="157"/>
       <c r="O37" s="54"/>
       <c r="P37" s="55"/>
     </row>
-    <row r="38" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B38" s="51"/>
-      <c r="C38" s="141" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142"/>
-      <c r="H38" s="142"/>
-      <c r="I38" s="142"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="142"/>
-      <c r="M38" s="142"/>
-      <c r="N38" s="143"/>
+      <c r="C38" s="126" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
+      <c r="J38" s="127"/>
+      <c r="K38" s="127"/>
+      <c r="L38" s="127"/>
+      <c r="M38" s="127"/>
+      <c r="N38" s="128"/>
       <c r="O38" s="54"/>
       <c r="P38" s="55"/>
     </row>
-    <row r="39" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="51"/>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="158" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="145"/>
-      <c r="E39" s="145"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="146"/>
-      <c r="H39" s="176" t="s">
-        <v>104</v>
-      </c>
-      <c r="I39" s="145"/>
-      <c r="J39" s="145"/>
-      <c r="K39" s="145"/>
-      <c r="L39" s="145"/>
-      <c r="M39" s="145"/>
-      <c r="N39" s="177"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="118"/>
+      <c r="M39" s="118"/>
+      <c r="N39" s="119"/>
       <c r="O39" s="54"/>
       <c r="P39" s="55"/>
     </row>
-    <row r="40" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="51"/>
-      <c r="C40" s="178" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="179"/>
-      <c r="E40" s="179"/>
-      <c r="F40" s="179"/>
-      <c r="G40" s="179"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
-      <c r="L40" s="179"/>
-      <c r="M40" s="179"/>
-      <c r="N40" s="180"/>
+      <c r="C40" s="120" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="121"/>
+      <c r="K40" s="121"/>
+      <c r="L40" s="121"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="122"/>
       <c r="O40" s="54"/>
       <c r="P40" s="55"/>
     </row>
-    <row r="41" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="51"/>
-      <c r="C41" s="181" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="182"/>
-      <c r="E41" s="182"/>
-      <c r="F41" s="182"/>
-      <c r="G41" s="182"/>
-      <c r="H41" s="182"/>
-      <c r="I41" s="182"/>
-      <c r="J41" s="182"/>
-      <c r="K41" s="182"/>
-      <c r="L41" s="182"/>
-      <c r="M41" s="182"/>
-      <c r="N41" s="183"/>
+      <c r="C41" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="124"/>
+      <c r="G41" s="124"/>
+      <c r="H41" s="124"/>
+      <c r="I41" s="124"/>
+      <c r="J41" s="124"/>
+      <c r="K41" s="124"/>
+      <c r="L41" s="124"/>
+      <c r="M41" s="124"/>
+      <c r="N41" s="125"/>
       <c r="O41" s="54"/>
       <c r="P41" s="55"/>
     </row>
-    <row r="42" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B42" s="51"/>
-      <c r="C42" s="141" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="142"/>
-      <c r="E42" s="142"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="142"/>
-      <c r="H42" s="142"/>
-      <c r="I42" s="142"/>
-      <c r="J42" s="142"/>
-      <c r="K42" s="142"/>
-      <c r="L42" s="142"/>
-      <c r="M42" s="142"/>
-      <c r="N42" s="143"/>
+      <c r="C42" s="126" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="127"/>
+      <c r="E42" s="127"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="127"/>
+      <c r="H42" s="127"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
+      <c r="K42" s="127"/>
+      <c r="L42" s="127"/>
+      <c r="M42" s="127"/>
+      <c r="N42" s="128"/>
       <c r="O42" s="54"/>
       <c r="P42" s="55"/>
     </row>
-    <row r="43" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="51"/>
-      <c r="C43" s="106" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="107"/>
-      <c r="G43" s="107"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="107"/>
-      <c r="J43" s="107"/>
-      <c r="K43" s="107"/>
-      <c r="L43" s="107"/>
-      <c r="M43" s="107"/>
-      <c r="N43" s="108"/>
+      <c r="C43" s="113" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="114"/>
+      <c r="E43" s="114"/>
+      <c r="F43" s="114"/>
+      <c r="G43" s="114"/>
+      <c r="H43" s="114"/>
+      <c r="I43" s="114"/>
+      <c r="J43" s="114"/>
+      <c r="K43" s="114"/>
+      <c r="L43" s="114"/>
+      <c r="M43" s="114"/>
+      <c r="N43" s="115"/>
       <c r="O43" s="54"/>
       <c r="P43" s="55"/>
     </row>
-    <row r="44" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B44" s="51"/>
-      <c r="C44" s="190" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="191"/>
-      <c r="E44" s="191"/>
-      <c r="F44" s="191"/>
-      <c r="G44" s="191"/>
-      <c r="H44" s="191"/>
-      <c r="I44" s="191"/>
-      <c r="J44" s="191"/>
-      <c r="K44" s="191"/>
-      <c r="L44" s="191"/>
-      <c r="M44" s="191"/>
-      <c r="N44" s="192"/>
+      <c r="C44" s="144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="145"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="145"/>
+      <c r="I44" s="145"/>
+      <c r="J44" s="145"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
+      <c r="M44" s="145"/>
+      <c r="N44" s="146"/>
       <c r="O44" s="54"/>
       <c r="P44" s="55"/>
     </row>
-    <row r="45" spans="2:16" s="2" customFormat="1" ht="101" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" s="2" customFormat="1" ht="100.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B45" s="51"/>
-      <c r="C45" s="109" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" s="110"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="110"/>
-      <c r="H45" s="110"/>
-      <c r="I45" s="110"/>
-      <c r="J45" s="110"/>
-      <c r="K45" s="110"/>
-      <c r="L45" s="110"/>
-      <c r="M45" s="110"/>
-      <c r="N45" s="111"/>
+      <c r="C45" s="184" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="185"/>
+      <c r="E45" s="185"/>
+      <c r="F45" s="185"/>
+      <c r="G45" s="185"/>
+      <c r="H45" s="185"/>
+      <c r="I45" s="185"/>
+      <c r="J45" s="185"/>
+      <c r="K45" s="185"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="185"/>
+      <c r="N45" s="186"/>
       <c r="O45" s="54"/>
       <c r="P45" s="55"/>
     </row>
-    <row r="46" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B46" s="51"/>
-      <c r="C46" s="103" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="104"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="104"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="104"/>
-      <c r="N46" s="105"/>
+      <c r="C46" s="107" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="108"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="109"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
     </row>
-    <row r="47" spans="2:16" s="2" customFormat="1" ht="59" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" s="2" customFormat="1" ht="58.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B47" s="51"/>
-      <c r="C47" s="106" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" s="107"/>
-      <c r="E47" s="107"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
-      <c r="H47" s="107"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="107"/>
-      <c r="K47" s="107"/>
-      <c r="L47" s="107"/>
-      <c r="M47" s="107"/>
-      <c r="N47" s="108"/>
+      <c r="C47" s="113" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" s="114"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="114"/>
+      <c r="G47" s="114"/>
+      <c r="H47" s="114"/>
+      <c r="I47" s="114"/>
+      <c r="J47" s="114"/>
+      <c r="K47" s="114"/>
+      <c r="L47" s="114"/>
+      <c r="M47" s="114"/>
+      <c r="N47" s="115"/>
       <c r="O47" s="54"/>
       <c r="P47" s="55"/>
     </row>
-    <row r="48" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="51"/>
-      <c r="C48" s="187" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="188"/>
-      <c r="E48" s="188"/>
-      <c r="F48" s="188"/>
-      <c r="G48" s="188"/>
-      <c r="H48" s="188"/>
-      <c r="I48" s="188"/>
-      <c r="J48" s="188"/>
-      <c r="K48" s="188"/>
-      <c r="L48" s="188"/>
-      <c r="M48" s="188"/>
-      <c r="N48" s="189"/>
+      <c r="C48" s="141" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" s="142"/>
+      <c r="E48" s="142"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="142"/>
+      <c r="I48" s="142"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="142"/>
+      <c r="L48" s="142"/>
+      <c r="M48" s="142"/>
+      <c r="N48" s="143"/>
       <c r="O48" s="54"/>
       <c r="P48" s="55"/>
     </row>
-    <row r="49" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B49" s="51"/>
-      <c r="C49" s="118" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="119"/>
-      <c r="H49" s="119"/>
-      <c r="I49" s="119"/>
-      <c r="J49" s="119"/>
-      <c r="K49" s="119"/>
-      <c r="L49" s="119"/>
-      <c r="M49" s="119"/>
-      <c r="N49" s="120"/>
+      <c r="C49" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="130"/>
+      <c r="E49" s="130"/>
+      <c r="F49" s="130"/>
+      <c r="G49" s="130"/>
+      <c r="H49" s="130"/>
+      <c r="I49" s="130"/>
+      <c r="J49" s="130"/>
+      <c r="K49" s="130"/>
+      <c r="L49" s="130"/>
+      <c r="M49" s="130"/>
+      <c r="N49" s="131"/>
       <c r="O49" s="54"/>
       <c r="P49" s="55"/>
     </row>
-    <row r="50" spans="2:16" s="2" customFormat="1" ht="39.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" s="2" customFormat="1" ht="39.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B50" s="51"/>
-      <c r="C50" s="130" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50" s="131"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="131"/>
-      <c r="G50" s="131"/>
-      <c r="H50" s="131"/>
-      <c r="I50" s="131"/>
-      <c r="J50" s="131"/>
-      <c r="K50" s="131"/>
-      <c r="L50" s="131"/>
-      <c r="M50" s="131"/>
-      <c r="N50" s="132"/>
+      <c r="C50" s="199" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="200"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="200"/>
+      <c r="H50" s="200"/>
+      <c r="I50" s="200"/>
+      <c r="J50" s="200"/>
+      <c r="K50" s="200"/>
+      <c r="L50" s="200"/>
+      <c r="M50" s="200"/>
+      <c r="N50" s="201"/>
       <c r="O50" s="54"/>
       <c r="P50" s="55"/>
     </row>
-    <row r="51" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B51" s="51"/>
-      <c r="C51" s="138" t="s">
-        <v>80</v>
-      </c>
-      <c r="D51" s="139"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="139"/>
-      <c r="I51" s="139"/>
-      <c r="J51" s="139"/>
-      <c r="K51" s="139"/>
-      <c r="L51" s="139"/>
-      <c r="M51" s="139"/>
-      <c r="N51" s="140"/>
+      <c r="C51" s="135" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="136"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="136"/>
+      <c r="G51" s="136"/>
+      <c r="H51" s="136"/>
+      <c r="I51" s="136"/>
+      <c r="J51" s="136"/>
+      <c r="K51" s="136"/>
+      <c r="L51" s="136"/>
+      <c r="M51" s="136"/>
+      <c r="N51" s="137"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
     </row>
-    <row r="52" spans="2:16" s="2" customFormat="1" ht="182" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" s="2" customFormat="1" ht="181.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B52" s="51"/>
-      <c r="C52" s="127" t="s">
-        <v>135</v>
-      </c>
-      <c r="D52" s="128"/>
-      <c r="E52" s="128"/>
-      <c r="F52" s="128"/>
-      <c r="G52" s="128"/>
-      <c r="H52" s="128"/>
-      <c r="I52" s="128"/>
-      <c r="J52" s="128"/>
-      <c r="K52" s="128"/>
-      <c r="L52" s="128"/>
-      <c r="M52" s="128"/>
-      <c r="N52" s="129"/>
+      <c r="C52" s="196" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" s="197"/>
+      <c r="E52" s="197"/>
+      <c r="F52" s="197"/>
+      <c r="G52" s="197"/>
+      <c r="H52" s="197"/>
+      <c r="I52" s="197"/>
+      <c r="J52" s="197"/>
+      <c r="K52" s="197"/>
+      <c r="L52" s="197"/>
+      <c r="M52" s="197"/>
+      <c r="N52" s="198"/>
       <c r="O52" s="54"/>
       <c r="P52" s="55"/>
     </row>
-    <row r="53" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B53" s="51"/>
-      <c r="C53" s="118" t="s">
-        <v>76</v>
-      </c>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="119"/>
-      <c r="K53" s="119"/>
-      <c r="L53" s="119"/>
-      <c r="M53" s="119"/>
-      <c r="N53" s="120"/>
+      <c r="C53" s="129" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="130"/>
+      <c r="E53" s="130"/>
+      <c r="F53" s="130"/>
+      <c r="G53" s="130"/>
+      <c r="H53" s="130"/>
+      <c r="I53" s="130"/>
+      <c r="J53" s="130"/>
+      <c r="K53" s="130"/>
+      <c r="L53" s="130"/>
+      <c r="M53" s="130"/>
+      <c r="N53" s="131"/>
       <c r="O53" s="54"/>
       <c r="P53" s="55"/>
     </row>
-    <row r="54" spans="2:16" s="2" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" s="2" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B54" s="51"/>
-      <c r="C54" s="184" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="185"/>
-      <c r="E54" s="185"/>
-      <c r="F54" s="185"/>
-      <c r="G54" s="185"/>
-      <c r="H54" s="185"/>
-      <c r="I54" s="185"/>
-      <c r="J54" s="185"/>
-      <c r="K54" s="185"/>
-      <c r="L54" s="185"/>
-      <c r="M54" s="185"/>
-      <c r="N54" s="186"/>
+      <c r="C54" s="132" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="133"/>
+      <c r="E54" s="133"/>
+      <c r="F54" s="133"/>
+      <c r="G54" s="133"/>
+      <c r="H54" s="133"/>
+      <c r="I54" s="133"/>
+      <c r="J54" s="133"/>
+      <c r="K54" s="133"/>
+      <c r="L54" s="133"/>
+      <c r="M54" s="133"/>
+      <c r="N54" s="134"/>
       <c r="O54" s="54"/>
       <c r="P54" s="55"/>
     </row>
-    <row r="55" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B55" s="51"/>
-      <c r="C55" s="138" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="139"/>
-      <c r="E55" s="139"/>
-      <c r="F55" s="139"/>
-      <c r="G55" s="139"/>
-      <c r="H55" s="139"/>
-      <c r="I55" s="139"/>
-      <c r="J55" s="139"/>
-      <c r="K55" s="139"/>
-      <c r="L55" s="139"/>
-      <c r="M55" s="139"/>
-      <c r="N55" s="140"/>
+      <c r="C55" s="135" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="136"/>
+      <c r="E55" s="136"/>
+      <c r="F55" s="136"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="136"/>
+      <c r="J55" s="136"/>
+      <c r="K55" s="136"/>
+      <c r="L55" s="136"/>
+      <c r="M55" s="136"/>
+      <c r="N55" s="137"/>
       <c r="O55" s="54"/>
       <c r="P55" s="55"/>
     </row>
-    <row r="56" spans="2:16" s="2" customFormat="1" ht="182" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" s="2" customFormat="1" ht="181.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="51"/>
-      <c r="C56" s="121" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" s="122"/>
-      <c r="E56" s="122"/>
-      <c r="F56" s="122"/>
-      <c r="G56" s="122"/>
-      <c r="H56" s="122"/>
-      <c r="I56" s="122"/>
-      <c r="J56" s="122"/>
-      <c r="K56" s="122"/>
-      <c r="L56" s="122"/>
-      <c r="M56" s="122"/>
-      <c r="N56" s="123"/>
+      <c r="C56" s="138" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" s="139"/>
+      <c r="E56" s="139"/>
+      <c r="F56" s="139"/>
+      <c r="G56" s="139"/>
+      <c r="H56" s="139"/>
+      <c r="I56" s="139"/>
+      <c r="J56" s="139"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="139"/>
+      <c r="M56" s="139"/>
+      <c r="N56" s="140"/>
       <c r="O56" s="54"/>
       <c r="P56" s="55"/>
     </row>
-    <row r="57" spans="2:16" s="2" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" s="2" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="51"/>
-      <c r="C57" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" s="116"/>
-      <c r="E57" s="116"/>
-      <c r="F57" s="116"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="116"/>
-      <c r="I57" s="116"/>
-      <c r="J57" s="116"/>
-      <c r="K57" s="116"/>
-      <c r="L57" s="116"/>
-      <c r="M57" s="116"/>
-      <c r="N57" s="117"/>
+      <c r="C57" s="190" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="191"/>
+      <c r="E57" s="191"/>
+      <c r="F57" s="191"/>
+      <c r="G57" s="191"/>
+      <c r="H57" s="191"/>
+      <c r="I57" s="191"/>
+      <c r="J57" s="191"/>
+      <c r="K57" s="191"/>
+      <c r="L57" s="191"/>
+      <c r="M57" s="191"/>
+      <c r="N57" s="192"/>
       <c r="O57" s="54"/>
       <c r="P57" s="55"/>
     </row>
-    <row r="58" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B58" s="51"/>
-      <c r="C58" s="118" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" s="119"/>
-      <c r="E58" s="119"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="119"/>
-      <c r="H58" s="119"/>
-      <c r="I58" s="119"/>
-      <c r="J58" s="119"/>
-      <c r="K58" s="119"/>
-      <c r="L58" s="119"/>
-      <c r="M58" s="119"/>
-      <c r="N58" s="120"/>
+      <c r="C58" s="129" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="130"/>
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="130"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="130"/>
+      <c r="J58" s="130"/>
+      <c r="K58" s="130"/>
+      <c r="L58" s="130"/>
+      <c r="M58" s="130"/>
+      <c r="N58" s="131"/>
       <c r="O58" s="54"/>
       <c r="P58" s="55"/>
     </row>
-    <row r="59" spans="2:16" s="2" customFormat="1" ht="230" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" s="2" customFormat="1" ht="229.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="51"/>
-      <c r="C59" s="121" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="122"/>
-      <c r="E59" s="122"/>
-      <c r="F59" s="122"/>
-      <c r="G59" s="122"/>
-      <c r="H59" s="122"/>
-      <c r="I59" s="122"/>
-      <c r="J59" s="122"/>
-      <c r="K59" s="122"/>
-      <c r="L59" s="122"/>
-      <c r="M59" s="122"/>
-      <c r="N59" s="123"/>
+      <c r="C59" s="138" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="139"/>
+      <c r="L59" s="139"/>
+      <c r="M59" s="139"/>
+      <c r="N59" s="140"/>
       <c r="O59" s="54"/>
       <c r="P59" s="55"/>
     </row>
-    <row r="60" spans="2:16" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="51"/>
-      <c r="C60" s="115" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="116"/>
-      <c r="E60" s="116"/>
-      <c r="F60" s="116"/>
-      <c r="G60" s="116"/>
-      <c r="H60" s="116"/>
-      <c r="I60" s="116"/>
-      <c r="J60" s="116"/>
-      <c r="K60" s="116"/>
-      <c r="L60" s="116"/>
-      <c r="M60" s="116"/>
-      <c r="N60" s="117"/>
+      <c r="C60" s="190" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="191"/>
+      <c r="E60" s="191"/>
+      <c r="F60" s="191"/>
+      <c r="G60" s="191"/>
+      <c r="H60" s="191"/>
+      <c r="I60" s="191"/>
+      <c r="J60" s="191"/>
+      <c r="K60" s="191"/>
+      <c r="L60" s="191"/>
+      <c r="M60" s="191"/>
+      <c r="N60" s="192"/>
       <c r="O60" s="54"/>
       <c r="P60" s="55"/>
     </row>
-    <row r="61" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B61" s="51"/>
-      <c r="C61" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="119"/>
-      <c r="H61" s="119"/>
-      <c r="I61" s="119"/>
-      <c r="J61" s="119"/>
-      <c r="K61" s="119"/>
-      <c r="L61" s="119"/>
-      <c r="M61" s="119"/>
-      <c r="N61" s="120"/>
+      <c r="C61" s="129" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="130"/>
+      <c r="E61" s="130"/>
+      <c r="F61" s="130"/>
+      <c r="G61" s="130"/>
+      <c r="H61" s="130"/>
+      <c r="I61" s="130"/>
+      <c r="J61" s="130"/>
+      <c r="K61" s="130"/>
+      <c r="L61" s="130"/>
+      <c r="M61" s="130"/>
+      <c r="N61" s="131"/>
       <c r="O61" s="54"/>
       <c r="P61" s="55"/>
     </row>
-    <row r="62" spans="2:16" s="2" customFormat="1" ht="87.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" s="2" customFormat="1" ht="87.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B62" s="51"/>
-      <c r="C62" s="124" t="s">
-        <v>138</v>
-      </c>
-      <c r="D62" s="125"/>
-      <c r="E62" s="125"/>
-      <c r="F62" s="125"/>
-      <c r="G62" s="125"/>
-      <c r="H62" s="125"/>
-      <c r="I62" s="125"/>
-      <c r="J62" s="125"/>
-      <c r="K62" s="125"/>
-      <c r="L62" s="125"/>
-      <c r="M62" s="125"/>
-      <c r="N62" s="126"/>
+      <c r="C62" s="193" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" s="194"/>
+      <c r="E62" s="194"/>
+      <c r="F62" s="194"/>
+      <c r="G62" s="194"/>
+      <c r="H62" s="194"/>
+      <c r="I62" s="194"/>
+      <c r="J62" s="194"/>
+      <c r="K62" s="194"/>
+      <c r="L62" s="194"/>
+      <c r="M62" s="194"/>
+      <c r="N62" s="195"/>
       <c r="O62" s="54"/>
       <c r="P62" s="55"/>
     </row>
-    <row r="63" spans="2:16" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B63" s="51"/>
-      <c r="C63" s="118" t="s">
-        <v>75</v>
-      </c>
-      <c r="D63" s="119"/>
-      <c r="E63" s="119"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="119"/>
-      <c r="H63" s="119"/>
-      <c r="I63" s="119"/>
-      <c r="J63" s="119"/>
-      <c r="K63" s="119"/>
-      <c r="L63" s="119"/>
-      <c r="M63" s="119"/>
-      <c r="N63" s="120"/>
+      <c r="C63" s="129" t="s">
+        <v>74</v>
+      </c>
+      <c r="D63" s="130"/>
+      <c r="E63" s="130"/>
+      <c r="F63" s="130"/>
+      <c r="G63" s="130"/>
+      <c r="H63" s="130"/>
+      <c r="I63" s="130"/>
+      <c r="J63" s="130"/>
+      <c r="K63" s="130"/>
+      <c r="L63" s="130"/>
+      <c r="M63" s="130"/>
+      <c r="N63" s="131"/>
       <c r="O63" s="54"/>
       <c r="P63" s="55"/>
     </row>
-    <row r="64" spans="2:16" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" s="2" customFormat="1" ht="27.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="51"/>
-      <c r="C64" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" s="101"/>
-      <c r="E64" s="101"/>
-      <c r="F64" s="101"/>
-      <c r="G64" s="101"/>
-      <c r="H64" s="101"/>
-      <c r="I64" s="101"/>
-      <c r="J64" s="101"/>
-      <c r="K64" s="101"/>
-      <c r="L64" s="101"/>
-      <c r="M64" s="101"/>
-      <c r="N64" s="102"/>
+      <c r="C64" s="181" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="182"/>
+      <c r="E64" s="182"/>
+      <c r="F64" s="182"/>
+      <c r="G64" s="182"/>
+      <c r="H64" s="182"/>
+      <c r="I64" s="182"/>
+      <c r="J64" s="182"/>
+      <c r="K64" s="182"/>
+      <c r="L64" s="182"/>
+      <c r="M64" s="182"/>
+      <c r="N64" s="183"/>
       <c r="O64" s="54"/>
       <c r="P64" s="55"/>
     </row>
-    <row r="65" spans="2:16" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:16" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="51"/>
-      <c r="C65" s="112"/>
-      <c r="D65" s="113"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="113"/>
-      <c r="G65" s="113"/>
-      <c r="I65" s="113"/>
-      <c r="J65" s="113"/>
-      <c r="K65" s="113"/>
-      <c r="L65" s="113"/>
-      <c r="M65" s="113"/>
-      <c r="N65" s="114"/>
+      <c r="C65" s="187"/>
+      <c r="D65" s="188"/>
+      <c r="E65" s="188"/>
+      <c r="F65" s="188"/>
+      <c r="G65" s="188"/>
+      <c r="I65" s="188"/>
+      <c r="J65" s="188"/>
+      <c r="K65" s="188"/>
+      <c r="L65" s="188"/>
+      <c r="M65" s="188"/>
+      <c r="N65" s="189"/>
       <c r="O65" s="45"/>
     </row>
-    <row r="66" spans="2:16" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:16" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" s="51"/>
       <c r="C66" s="61"/>
       <c r="D66" s="56"/>
@@ -6063,45 +5913,45 @@
       <c r="N66" s="63"/>
       <c r="O66" s="45"/>
     </row>
-    <row r="67" spans="2:16" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:16" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="51"/>
-      <c r="C67" s="193" t="s">
+      <c r="C67" s="147" t="s">
+        <v>110</v>
+      </c>
+      <c r="D67" s="148"/>
+      <c r="E67" s="148"/>
+      <c r="F67" s="148"/>
+      <c r="G67" s="148"/>
+      <c r="I67" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="194"/>
-      <c r="E67" s="194"/>
-      <c r="F67" s="194"/>
-      <c r="G67" s="194"/>
-      <c r="I67" s="194" t="s">
-        <v>112</v>
-      </c>
-      <c r="J67" s="194"/>
-      <c r="K67" s="194"/>
-      <c r="L67" s="194"/>
-      <c r="M67" s="194"/>
-      <c r="N67" s="195"/>
+      <c r="J67" s="148"/>
+      <c r="K67" s="148"/>
+      <c r="L67" s="148"/>
+      <c r="M67" s="148"/>
+      <c r="N67" s="149"/>
       <c r="O67" s="45"/>
     </row>
-    <row r="68" spans="2:16" ht="47" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:16" ht="46.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="44"/>
-      <c r="C68" s="97" t="s">
-        <v>139</v>
-      </c>
-      <c r="D68" s="98"/>
-      <c r="E68" s="98"/>
-      <c r="F68" s="98"/>
-      <c r="G68" s="98"/>
-      <c r="H68" s="98"/>
-      <c r="I68" s="98"/>
-      <c r="J68" s="98"/>
-      <c r="K68" s="98"/>
-      <c r="L68" s="98"/>
-      <c r="M68" s="98"/>
-      <c r="N68" s="99"/>
+      <c r="C68" s="178" t="s">
+        <v>137</v>
+      </c>
+      <c r="D68" s="179"/>
+      <c r="E68" s="179"/>
+      <c r="F68" s="179"/>
+      <c r="G68" s="179"/>
+      <c r="H68" s="179"/>
+      <c r="I68" s="179"/>
+      <c r="J68" s="179"/>
+      <c r="K68" s="179"/>
+      <c r="L68" s="179"/>
+      <c r="M68" s="179"/>
+      <c r="N68" s="180"/>
       <c r="O68" s="40"/>
       <c r="P68" s="41"/>
     </row>
-    <row r="69" spans="2:16" s="2" customFormat="1" ht="9.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:16" s="2" customFormat="1" ht="9.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="51"/>
       <c r="C69" s="42"/>
       <c r="D69" s="42"/>
@@ -6117,37 +5967,72 @@
       <c r="N69" s="42"/>
       <c r="O69" s="45"/>
     </row>
-    <row r="70" spans="2:16" s="2" customFormat="1" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" s="2" customFormat="1" ht="22.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B70" s="57"/>
-      <c r="C70" s="175" t="s">
-        <v>113</v>
-      </c>
-      <c r="D70" s="175"/>
-      <c r="E70" s="175"/>
-      <c r="F70" s="175"/>
-      <c r="G70" s="175"/>
-      <c r="H70" s="175"/>
-      <c r="I70" s="175"/>
-      <c r="J70" s="175"/>
-      <c r="K70" s="175"/>
-      <c r="L70" s="175"/>
-      <c r="M70" s="175"/>
-      <c r="N70" s="175"/>
+      <c r="C70" s="116" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="116"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="116"/>
+      <c r="G70" s="116"/>
+      <c r="H70" s="116"/>
+      <c r="I70" s="116"/>
+      <c r="J70" s="116"/>
+      <c r="K70" s="116"/>
+      <c r="L70" s="116"/>
+      <c r="M70" s="116"/>
+      <c r="N70" s="116"/>
       <c r="O70" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="C2:M2"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="C10:N10"/>
-    <mergeCell ref="C21:N21"/>
-    <mergeCell ref="C23:N23"/>
-    <mergeCell ref="C22:N22"/>
+    <mergeCell ref="C68:N68"/>
+    <mergeCell ref="C64:N64"/>
+    <mergeCell ref="C46:N46"/>
+    <mergeCell ref="C47:N47"/>
+    <mergeCell ref="C45:N45"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="I65:N65"/>
+    <mergeCell ref="C57:N57"/>
+    <mergeCell ref="C58:N58"/>
+    <mergeCell ref="C59:N59"/>
+    <mergeCell ref="C60:N60"/>
+    <mergeCell ref="C63:N63"/>
+    <mergeCell ref="C61:N61"/>
+    <mergeCell ref="C62:N62"/>
+    <mergeCell ref="C52:N52"/>
+    <mergeCell ref="C50:N50"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="C32:N32"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="C38:N38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C30:N30"/>
+    <mergeCell ref="C33:N33"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C5:N5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C35:N35"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="D8:N8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C16:N16"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="C37:N37"/>
+    <mergeCell ref="C24:N24"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="M29:N29"/>
     <mergeCell ref="C70:N70"/>
     <mergeCell ref="H39:N39"/>
     <mergeCell ref="C40:N40"/>
@@ -6164,55 +6049,21 @@
     <mergeCell ref="C67:G67"/>
     <mergeCell ref="I67:N67"/>
     <mergeCell ref="C55:N55"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="C37:N37"/>
-    <mergeCell ref="C24:N24"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="C38:N38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C30:N30"/>
-    <mergeCell ref="C33:N33"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C5:N5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C35:N35"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="C7:N7"/>
-    <mergeCell ref="D8:N8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C16:N16"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="C32:N32"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="C68:N68"/>
-    <mergeCell ref="C64:N64"/>
-    <mergeCell ref="C46:N46"/>
-    <mergeCell ref="C47:N47"/>
-    <mergeCell ref="C45:N45"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="I65:N65"/>
-    <mergeCell ref="C57:N57"/>
-    <mergeCell ref="C58:N58"/>
-    <mergeCell ref="C59:N59"/>
-    <mergeCell ref="C60:N60"/>
-    <mergeCell ref="C63:N63"/>
-    <mergeCell ref="C61:N61"/>
-    <mergeCell ref="C62:N62"/>
-    <mergeCell ref="C52:N52"/>
-    <mergeCell ref="C50:N50"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="C10:N10"/>
+    <mergeCell ref="C21:N21"/>
+    <mergeCell ref="C23:N23"/>
+    <mergeCell ref="C22:N22"/>
   </mergeCells>
-  <pageMargins left="0.43" right="0.26" top="0.45" bottom="0.46" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="62" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="79" fitToHeight="3" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -6220,51 +6071,7 @@
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9227" r:id="rId4" name="Check Box 11">
-              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor>
-                  <from>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>7</xdr:col>
-                    <xdr:colOff>635000</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="9228" r:id="rId5" name="Check Box 12">
-              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor>
-                  <from>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>114300</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>12</xdr:col>
-                    <xdr:colOff>635000</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>76200</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="9229" r:id="rId6" name="Check Box 9">
+            <control shapeId="9229" r:id="rId4" name="Check Box 9">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -6275,9 +6082,9 @@
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
+                    <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6286,7 +6093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9230" r:id="rId7" name="Check Box 9">
+            <control shapeId="9230" r:id="rId5" name="Check Box 14">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -6299,7 +6106,7 @@
                     <xdr:col>8</xdr:col>
                     <xdr:colOff>38100</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
+                    <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6308,18 +6115,18 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9231" r:id="rId8" name="Check Box 9">
+            <control shapeId="9231" r:id="rId6" name="Check Box 15">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>101600</xdr:colOff>
+                    <xdr:colOff>99060</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>406400</xdr:colOff>
+                    <xdr:colOff>403860</xdr:colOff>
                     <xdr:row>36</xdr:row>
                     <xdr:rowOff>190500</xdr:rowOff>
                   </to>
@@ -6330,20 +6137,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9232" r:id="rId9" name="Check Box 9">
+            <control shapeId="9232" r:id="rId7" name="Check Box 16">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>88900</xdr:colOff>
+                    <xdr:colOff>91440</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>101600</xdr:colOff>
+                    <xdr:colOff>99060</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6352,20 +6159,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9233" r:id="rId10" name="Check Box 9">
+            <control shapeId="9233" r:id="rId8" name="Check Box 17">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>8</xdr:col>
-                    <xdr:colOff>25400</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>9</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>12700</xdr:rowOff>
+                    <xdr:rowOff>15240</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6374,20 +6181,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9234" r:id="rId11" name="Check Box 9">
+            <control shapeId="9234" r:id="rId9" name="Check Box 18">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>12</xdr:col>
                     <xdr:colOff>114300</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>12</xdr:col>
-                    <xdr:colOff>444500</xdr:colOff>
+                    <xdr:colOff>441960</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6396,18 +6203,18 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9235" r:id="rId12" name="Check Box 19">
+            <control shapeId="9235" r:id="rId10" name="Check Box 19">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>203200</xdr:colOff>
+                    <xdr:colOff>205740</xdr:colOff>
                     <xdr:row>41</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>7</xdr:col>
-                    <xdr:colOff>127000</xdr:colOff>
+                    <xdr:colOff>129540</xdr:colOff>
                     <xdr:row>43</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -6418,18 +6225,18 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9236" r:id="rId13" name="Check Box 20">
+            <control shapeId="9236" r:id="rId11" name="Check Box 20">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>11</xdr:col>
                     <xdr:colOff>495300</xdr:colOff>
                     <xdr:row>41</xdr:row>
-                    <xdr:rowOff>177800</xdr:rowOff>
+                    <xdr:rowOff>175260</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>12</xdr:col>
-                    <xdr:colOff>63500</xdr:colOff>
+                    <xdr:colOff>60960</xdr:colOff>
                     <xdr:row>43</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -6440,12 +6247,12 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9237" r:id="rId14" name="Check Box 9">
+            <control shapeId="9237" r:id="rId12" name="Check Box 21">
               <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>444500</xdr:colOff>
+                    <xdr:colOff>441960</xdr:colOff>
                     <xdr:row>33</xdr:row>
                     <xdr:rowOff>114300</xdr:rowOff>
                   </from>
@@ -6453,7 +6260,7 @@
                     <xdr:col>7</xdr:col>
                     <xdr:colOff>304800</xdr:colOff>
                     <xdr:row>37</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6462,20 +6269,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9238" r:id="rId15" name="Check Box 22">
+            <control shapeId="9238" r:id="rId13" name="Check Box 22">
               <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor>
                   <from>
                     <xdr:col>7</xdr:col>
-                    <xdr:colOff>165100</xdr:colOff>
+                    <xdr:colOff>167640</xdr:colOff>
                     <xdr:row>19</xdr:row>
-                    <xdr:rowOff>127000</xdr:rowOff>
+                    <xdr:rowOff>129540</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>7</xdr:col>
-                    <xdr:colOff>635000</xdr:colOff>
+                    <xdr:colOff>632460</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>25400</xdr:rowOff>
+                    <xdr:rowOff>22860</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6484,20 +6291,20 @@
         </mc:AlternateContent>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="9239" r:id="rId16" name="Check Box 23">
+            <control shapeId="9239" r:id="rId14" name="Check Box 23">
               <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
                 <anchor>
                   <from>
                     <xdr:col>12</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>19</xdr:row>
                     <xdr:rowOff>114300</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>12</xdr:col>
-                    <xdr:colOff>635000</xdr:colOff>
+                    <xdr:colOff>632460</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>50800</xdr:rowOff>
+                    <xdr:rowOff>53340</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6513,79 +6320,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C1:T50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.1796875" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="6.81640625" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" customWidth="1"/>
-    <col min="8" max="8" width="1.81640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" customWidth="1"/>
+    <col min="8" max="8" width="1.77734375" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
-    <col min="11" max="11" width="3.36328125" customWidth="1"/>
-    <col min="12" max="12" width="5.81640625" customWidth="1"/>
-    <col min="13" max="13" width="11.6328125" customWidth="1"/>
-    <col min="14" max="14" width="3.453125" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" style="18"/>
-    <col min="19" max="19" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" customWidth="1"/>
+    <col min="14" max="14" width="3.44140625" customWidth="1"/>
+    <col min="16" max="16" width="10.77734375" style="18"/>
+    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D2" s="211" t="s">
+    <row r="1" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="236" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="212"/>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="208" t="s">
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="210"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="235"/>
       <c r="M2" s="19"/>
       <c r="N2" s="19"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D3" s="214"/>
-      <c r="E3" s="215"/>
-      <c r="F3" s="215"/>
-      <c r="G3" s="215"/>
-      <c r="H3" s="216"/>
+    <row r="3" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="239"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
+      <c r="G3" s="240"/>
+      <c r="H3" s="241"/>
       <c r="I3" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="204" t="s">
+      <c r="J3" s="229" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="204"/>
-      <c r="L3" s="205"/>
+      <c r="K3" s="229"/>
+      <c r="L3" s="230"/>
       <c r="O3" s="21"/>
     </row>
-    <row r="4" spans="3:15" ht="13.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D4" s="217"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="219"/>
+    <row r="4" spans="3:15" ht="13.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="242"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="244"/>
       <c r="I4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="231" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="206"/>
-      <c r="L4" s="207"/>
+      <c r="K4" s="231"/>
+      <c r="L4" s="232"/>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" spans="3:15" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:15" ht="6.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -6599,24 +6406,24 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="14"/>
-      <c r="D6" s="238" t="s">
+      <c r="D6" s="261" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="239"/>
-    </row>
-    <row r="7" spans="3:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E6" s="261"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
+      <c r="H6" s="261"/>
+      <c r="I6" s="261"/>
+      <c r="J6" s="261"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="261"/>
+      <c r="M6" s="261"/>
+      <c r="N6" s="261"/>
+      <c r="O6" s="262"/>
+    </row>
+    <row r="7" spans="3:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="14"/>
       <c r="D7" s="12" t="s">
         <v>1</v>
@@ -6624,15 +6431,15 @@
       <c r="E7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="247">
+      <c r="F7" s="220">
         <v>1121310100012</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="249"/>
-      <c r="I7" s="246" t="s">
+      <c r="G7" s="221"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="219" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="221"/>
+      <c r="J7" s="214"/>
       <c r="K7" s="35" t="s">
         <v>14</v>
       </c>
@@ -6647,7 +6454,7 @@
         <v>41961</v>
       </c>
     </row>
-    <row r="8" spans="3:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:15" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="C8" s="14"/>
       <c r="D8" s="13" t="s">
         <v>3</v>
@@ -6655,15 +6462,15 @@
       <c r="E8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="247">
+      <c r="F8" s="220">
         <v>1121310100012</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="246" t="s">
+      <c r="G8" s="221"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="219" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="221"/>
+      <c r="J8" s="214"/>
       <c r="K8" s="35" t="s">
         <v>14</v>
       </c>
@@ -6680,68 +6487,68 @@
         <v>41961</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C9" s="14"/>
       <c r="D9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="250" t="s">
+      <c r="E9" s="217" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="251"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="218"/>
       <c r="I9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="250" t="s">
+      <c r="K9" s="217" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="250"/>
-      <c r="M9" s="250"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="251"/>
-    </row>
-    <row r="10" spans="3:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="217"/>
+      <c r="M9" s="217"/>
+      <c r="N9" s="217"/>
+      <c r="O9" s="218"/>
+    </row>
+    <row r="10" spans="3:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="14"/>
-      <c r="D10" s="238" t="s">
+      <c r="D10" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="238"/>
-      <c r="O10" s="239"/>
-    </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="E10" s="261"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
+      <c r="H10" s="261"/>
+      <c r="I10" s="261"/>
+      <c r="J10" s="261"/>
+      <c r="K10" s="261"/>
+      <c r="L10" s="261"/>
+      <c r="M10" s="261"/>
+      <c r="N10" s="261"/>
+      <c r="O10" s="262"/>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C11" s="14"/>
       <c r="D11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="236"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="236"/>
-      <c r="H11" s="237"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="259"/>
+      <c r="G11" s="259"/>
+      <c r="H11" s="260"/>
       <c r="I11" s="11" t="s">
         <v>5</v>
       </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="224"/>
-      <c r="L11" s="224"/>
-      <c r="M11" s="235" t="s">
+      <c r="K11" s="247"/>
+      <c r="L11" s="247"/>
+      <c r="M11" s="258" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="236"/>
-      <c r="O11" s="237"/>
-    </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="N11" s="259"/>
+      <c r="O11" s="260"/>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="D12" s="11" t="s">
         <v>9</v>
@@ -6762,7 +6569,7 @@
       <c r="N12" s="7"/>
       <c r="O12" s="8"/>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
       <c r="D13" s="11" t="s">
         <v>11</v>
@@ -6779,7 +6586,7 @@
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
     </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C14" s="14"/>
       <c r="D14" s="11" t="s">
         <v>43</v>
@@ -6800,7 +6607,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="9"/>
     </row>
-    <row r="15" spans="3:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -6814,79 +6621,79 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="3:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="14"/>
-      <c r="D16" s="222" t="s">
+      <c r="D16" s="245" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="222"/>
-      <c r="F16" s="222"/>
-      <c r="G16" s="222"/>
-      <c r="H16" s="222"/>
-      <c r="I16" s="222"/>
-      <c r="J16" s="222"/>
-      <c r="K16" s="222"/>
-      <c r="L16" s="222"/>
-      <c r="M16" s="222"/>
-      <c r="N16" s="222"/>
-      <c r="O16" s="223"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="E16" s="245"/>
+      <c r="F16" s="245"/>
+      <c r="G16" s="245"/>
+      <c r="H16" s="245"/>
+      <c r="I16" s="245"/>
+      <c r="J16" s="245"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
+      <c r="M16" s="245"/>
+      <c r="N16" s="245"/>
+      <c r="O16" s="246"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C17" s="14"/>
-      <c r="D17" s="224" t="s">
+      <c r="D17" s="247" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="224"/>
-      <c r="F17" s="224"/>
-      <c r="G17" s="224"/>
-      <c r="H17" s="225"/>
-      <c r="I17" s="226" t="s">
+      <c r="E17" s="247"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="249" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="224"/>
-      <c r="K17" s="224"/>
-      <c r="L17" s="224"/>
-      <c r="M17" s="224"/>
-      <c r="N17" s="224"/>
-      <c r="O17" s="225"/>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="J17" s="247"/>
+      <c r="K17" s="247"/>
+      <c r="L17" s="247"/>
+      <c r="M17" s="247"/>
+      <c r="N17" s="247"/>
+      <c r="O17" s="248"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18" s="14"/>
-      <c r="D18" s="233" t="s">
+      <c r="D18" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="234"/>
-      <c r="I18" s="227" t="s">
+      <c r="E18" s="256"/>
+      <c r="F18" s="256"/>
+      <c r="G18" s="256"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="250" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="228"/>
-      <c r="K18" s="228"/>
-      <c r="L18" s="228"/>
-      <c r="M18" s="228"/>
-      <c r="N18" s="228"/>
-      <c r="O18" s="229"/>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
+      <c r="M18" s="251"/>
+      <c r="N18" s="251"/>
+      <c r="O18" s="252"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C19" s="14"/>
-      <c r="D19" s="233" t="s">
+      <c r="D19" s="256" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="233"/>
-      <c r="F19" s="233"/>
-      <c r="G19" s="233"/>
-      <c r="H19" s="234"/>
-      <c r="I19" s="230"/>
-      <c r="J19" s="231"/>
-      <c r="K19" s="231"/>
-      <c r="L19" s="231"/>
-      <c r="M19" s="231"/>
-      <c r="N19" s="231"/>
-      <c r="O19" s="232"/>
-    </row>
-    <row r="20" spans="3:20" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E19" s="256"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="256"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="253"/>
+      <c r="J19" s="254"/>
+      <c r="K19" s="254"/>
+      <c r="L19" s="254"/>
+      <c r="M19" s="254"/>
+      <c r="N19" s="254"/>
+      <c r="O19" s="255"/>
+    </row>
+    <row r="20" spans="3:20" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -6900,65 +6707,65 @@
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="D21" s="261" t="s">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="D21" s="211" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="261"/>
-      <c r="F21" s="261"/>
-      <c r="G21" s="261"/>
-      <c r="H21" s="261"/>
-      <c r="I21" s="261"/>
-      <c r="J21" s="261"/>
-      <c r="K21" s="261"/>
-      <c r="L21" s="261"/>
-      <c r="M21" s="261"/>
-      <c r="N21" s="261"/>
-      <c r="O21" s="262"/>
-    </row>
-    <row r="22" spans="3:20" ht="24" x14ac:dyDescent="0.35">
+      <c r="E21" s="211"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="211"/>
+      <c r="K21" s="211"/>
+      <c r="L21" s="211"/>
+      <c r="M21" s="211"/>
+      <c r="N21" s="211"/>
+      <c r="O21" s="212"/>
+    </row>
+    <row r="22" spans="3:20" ht="24" x14ac:dyDescent="0.3">
       <c r="D22" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="220" t="s">
+      <c r="E22" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="263"/>
-      <c r="G22" s="264"/>
-      <c r="H22" s="220" t="s">
+      <c r="F22" s="215"/>
+      <c r="G22" s="216"/>
+      <c r="H22" s="213" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="263"/>
-      <c r="J22" s="263"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="220" t="s">
+      <c r="I22" s="215"/>
+      <c r="J22" s="215"/>
+      <c r="K22" s="216"/>
+      <c r="L22" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="M22" s="264"/>
-      <c r="N22" s="220" t="s">
+      <c r="M22" s="216"/>
+      <c r="N22" s="213" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="221"/>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O22" s="214"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D23" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="258">
+      <c r="E23" s="208">
         <v>150000</v>
       </c>
-      <c r="F23" s="259"/>
-      <c r="G23" s="260"/>
-      <c r="H23" s="255" t="s">
+      <c r="F23" s="209"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="256"/>
-      <c r="J23" s="256"/>
-      <c r="K23" s="257"/>
-      <c r="L23" s="258">
+      <c r="I23" s="206"/>
+      <c r="J23" s="206"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="208">
         <v>6000</v>
       </c>
-      <c r="M23" s="260"/>
+      <c r="M23" s="210"/>
       <c r="N23" s="16"/>
       <c r="O23" s="17"/>
       <c r="P23" s="34"/>
@@ -6966,25 +6773,25 @@
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D24" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="258">
+      <c r="E24" s="208">
         <v>500000</v>
       </c>
-      <c r="F24" s="259"/>
-      <c r="G24" s="260"/>
-      <c r="H24" s="255" t="s">
+      <c r="F24" s="209"/>
+      <c r="G24" s="210"/>
+      <c r="H24" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I24" s="256"/>
-      <c r="J24" s="256"/>
-      <c r="K24" s="257"/>
-      <c r="L24" s="258">
+      <c r="I24" s="206"/>
+      <c r="J24" s="206"/>
+      <c r="K24" s="207"/>
+      <c r="L24" s="208">
         <v>17500</v>
       </c>
-      <c r="M24" s="260"/>
+      <c r="M24" s="210"/>
       <c r="N24" s="16"/>
       <c r="O24" s="17"/>
       <c r="P24" s="34"/>
@@ -6992,25 +6799,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D25" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="258">
+      <c r="E25" s="208">
         <v>500000</v>
       </c>
-      <c r="F25" s="259"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="255" t="s">
+      <c r="F25" s="209"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I25" s="256"/>
-      <c r="J25" s="256"/>
-      <c r="K25" s="257"/>
-      <c r="L25" s="258">
+      <c r="I25" s="206"/>
+      <c r="J25" s="206"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="208">
         <v>21500</v>
       </c>
-      <c r="M25" s="260"/>
+      <c r="M25" s="210"/>
       <c r="N25" s="26"/>
       <c r="O25" s="27"/>
       <c r="P25" s="34"/>
@@ -7018,295 +6825,295 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D26" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="258">
+      <c r="E26" s="208">
         <v>625000</v>
       </c>
-      <c r="F26" s="259"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="255" t="s">
+      <c r="F26" s="209"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I26" s="256"/>
-      <c r="J26" s="256"/>
-      <c r="K26" s="257"/>
-      <c r="L26" s="258">
+      <c r="I26" s="206"/>
+      <c r="J26" s="206"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="208">
         <v>27500</v>
       </c>
-      <c r="M26" s="260"/>
+      <c r="M26" s="210"/>
       <c r="N26" s="16"/>
       <c r="O26" s="17"/>
       <c r="Q26" s="38">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D27" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="258">
+      <c r="E27" s="208">
         <v>625000</v>
       </c>
-      <c r="F27" s="259"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="255" t="s">
+      <c r="F27" s="209"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I27" s="256"/>
-      <c r="J27" s="256"/>
-      <c r="K27" s="257"/>
-      <c r="L27" s="258">
+      <c r="I27" s="206"/>
+      <c r="J27" s="206"/>
+      <c r="K27" s="207"/>
+      <c r="L27" s="208">
         <v>31500</v>
       </c>
-      <c r="M27" s="260"/>
+      <c r="M27" s="210"/>
       <c r="N27" s="5"/>
       <c r="O27" s="6"/>
       <c r="Q27" s="38">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D28" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="258">
+      <c r="E28" s="208">
         <v>625000</v>
       </c>
-      <c r="F28" s="259"/>
-      <c r="G28" s="260"/>
-      <c r="H28" s="255" t="s">
+      <c r="F28" s="209"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I28" s="256"/>
-      <c r="J28" s="256"/>
-      <c r="K28" s="257"/>
-      <c r="L28" s="258">
+      <c r="I28" s="206"/>
+      <c r="J28" s="206"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="208">
         <v>35000</v>
       </c>
-      <c r="M28" s="260"/>
+      <c r="M28" s="210"/>
       <c r="N28" s="5"/>
       <c r="O28" s="6"/>
       <c r="Q28" s="38"/>
     </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C29" s="14"/>
-      <c r="D29" s="261" t="s">
+      <c r="D29" s="211" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="261"/>
-      <c r="F29" s="261"/>
-      <c r="G29" s="261"/>
-      <c r="H29" s="261"/>
-      <c r="I29" s="261"/>
-      <c r="J29" s="261"/>
-      <c r="K29" s="261"/>
-      <c r="L29" s="261"/>
-      <c r="M29" s="261"/>
-      <c r="N29" s="261"/>
-      <c r="O29" s="262"/>
+      <c r="E29" s="211"/>
+      <c r="F29" s="211"/>
+      <c r="G29" s="211"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="211"/>
+      <c r="J29" s="211"/>
+      <c r="K29" s="211"/>
+      <c r="L29" s="211"/>
+      <c r="M29" s="211"/>
+      <c r="N29" s="211"/>
+      <c r="O29" s="212"/>
       <c r="Q29" s="38"/>
     </row>
-    <row r="30" spans="3:20" ht="24" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:20" ht="24" x14ac:dyDescent="0.3">
       <c r="D30" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="220" t="s">
+      <c r="E30" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="263"/>
-      <c r="G30" s="264"/>
-      <c r="H30" s="220" t="s">
+      <c r="F30" s="215"/>
+      <c r="G30" s="216"/>
+      <c r="H30" s="213" t="s">
         <v>48</v>
       </c>
-      <c r="I30" s="263"/>
-      <c r="J30" s="263"/>
-      <c r="K30" s="264"/>
-      <c r="L30" s="220" t="s">
+      <c r="I30" s="215"/>
+      <c r="J30" s="215"/>
+      <c r="K30" s="216"/>
+      <c r="L30" s="213" t="s">
         <v>49</v>
       </c>
-      <c r="M30" s="264"/>
-      <c r="N30" s="220" t="s">
+      <c r="M30" s="216"/>
+      <c r="N30" s="213" t="s">
         <v>25</v>
       </c>
-      <c r="O30" s="221"/>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O30" s="214"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D31" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="252">
+      <c r="E31" s="202">
         <v>300</v>
       </c>
-      <c r="F31" s="254"/>
-      <c r="G31" s="253"/>
-      <c r="H31" s="255" t="s">
+      <c r="F31" s="203"/>
+      <c r="G31" s="204"/>
+      <c r="H31" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I31" s="256"/>
-      <c r="J31" s="256"/>
-      <c r="K31" s="257"/>
-      <c r="L31" s="252">
+      <c r="I31" s="206"/>
+      <c r="J31" s="206"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="202">
         <v>12</v>
       </c>
-      <c r="M31" s="253"/>
+      <c r="M31" s="204"/>
       <c r="N31" s="16"/>
       <c r="O31" s="17"/>
       <c r="P31" s="34"/>
       <c r="S31" s="18"/>
       <c r="T31" s="18"/>
     </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D32" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="252">
+      <c r="E32" s="202">
         <v>1000</v>
       </c>
-      <c r="F32" s="254"/>
-      <c r="G32" s="253"/>
-      <c r="H32" s="255" t="s">
+      <c r="F32" s="203"/>
+      <c r="G32" s="204"/>
+      <c r="H32" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I32" s="256"/>
-      <c r="J32" s="256"/>
-      <c r="K32" s="257"/>
-      <c r="L32" s="252">
+      <c r="I32" s="206"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="207"/>
+      <c r="L32" s="202">
         <v>35</v>
       </c>
-      <c r="M32" s="253"/>
+      <c r="M32" s="204"/>
       <c r="N32" s="16"/>
       <c r="O32" s="17"/>
       <c r="S32" s="18"/>
       <c r="T32" s="18"/>
     </row>
-    <row r="33" spans="4:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D33" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="252">
+      <c r="E33" s="202">
         <v>1000</v>
       </c>
-      <c r="F33" s="254"/>
-      <c r="G33" s="253"/>
-      <c r="H33" s="255" t="s">
+      <c r="F33" s="203"/>
+      <c r="G33" s="204"/>
+      <c r="H33" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I33" s="256"/>
-      <c r="J33" s="256"/>
-      <c r="K33" s="257"/>
-      <c r="L33" s="252">
+      <c r="I33" s="206"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="207"/>
+      <c r="L33" s="202">
         <v>43</v>
       </c>
-      <c r="M33" s="253"/>
+      <c r="M33" s="204"/>
       <c r="N33" s="26"/>
       <c r="O33" s="27"/>
       <c r="S33" s="18"/>
       <c r="T33" s="18"/>
     </row>
-    <row r="34" spans="4:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D34" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="252">
+      <c r="E34" s="202">
         <v>1250</v>
       </c>
-      <c r="F34" s="254"/>
-      <c r="G34" s="253"/>
-      <c r="H34" s="255" t="s">
+      <c r="F34" s="203"/>
+      <c r="G34" s="204"/>
+      <c r="H34" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I34" s="256"/>
-      <c r="J34" s="256"/>
-      <c r="K34" s="257"/>
-      <c r="L34" s="252">
+      <c r="I34" s="206"/>
+      <c r="J34" s="206"/>
+      <c r="K34" s="207"/>
+      <c r="L34" s="202">
         <v>55</v>
       </c>
-      <c r="M34" s="253"/>
+      <c r="M34" s="204"/>
       <c r="N34" s="16"/>
       <c r="O34" s="17"/>
       <c r="S34" s="18"/>
       <c r="T34" s="18"/>
     </row>
-    <row r="35" spans="4:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D35" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="252">
+      <c r="E35" s="202">
         <v>1250</v>
       </c>
-      <c r="F35" s="254"/>
-      <c r="G35" s="253"/>
-      <c r="H35" s="255" t="s">
+      <c r="F35" s="203"/>
+      <c r="G35" s="204"/>
+      <c r="H35" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="256"/>
-      <c r="J35" s="256"/>
-      <c r="K35" s="257"/>
-      <c r="L35" s="252">
+      <c r="I35" s="206"/>
+      <c r="J35" s="206"/>
+      <c r="K35" s="207"/>
+      <c r="L35" s="202">
         <v>63</v>
       </c>
-      <c r="M35" s="253"/>
+      <c r="M35" s="204"/>
       <c r="N35" s="5"/>
       <c r="O35" s="6"/>
     </row>
-    <row r="36" spans="4:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D36" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="252">
+      <c r="E36" s="202">
         <v>1250</v>
       </c>
-      <c r="F36" s="254"/>
-      <c r="G36" s="253"/>
-      <c r="H36" s="255" t="s">
+      <c r="F36" s="203"/>
+      <c r="G36" s="204"/>
+      <c r="H36" s="205" t="s">
         <v>55</v>
       </c>
-      <c r="I36" s="256"/>
-      <c r="J36" s="256"/>
-      <c r="K36" s="257"/>
-      <c r="L36" s="252">
+      <c r="I36" s="206"/>
+      <c r="J36" s="206"/>
+      <c r="K36" s="207"/>
+      <c r="L36" s="202">
         <v>70</v>
       </c>
-      <c r="M36" s="253"/>
+      <c r="M36" s="204"/>
       <c r="N36" s="5"/>
       <c r="O36" s="6"/>
     </row>
-    <row r="37" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="243" t="s">
+    <row r="37" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="226" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="243"/>
-      <c r="F37" s="243"/>
-      <c r="G37" s="243"/>
-      <c r="H37" s="243"/>
-      <c r="I37" s="243"/>
-      <c r="J37" s="243"/>
-      <c r="K37" s="243"/>
-      <c r="L37" s="243"/>
-      <c r="M37" s="243"/>
-      <c r="N37" s="243"/>
-      <c r="O37" s="243"/>
-    </row>
-    <row r="38" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="243" t="s">
+      <c r="E37" s="226"/>
+      <c r="F37" s="226"/>
+      <c r="G37" s="226"/>
+      <c r="H37" s="226"/>
+      <c r="I37" s="226"/>
+      <c r="J37" s="226"/>
+      <c r="K37" s="226"/>
+      <c r="L37" s="226"/>
+      <c r="M37" s="226"/>
+      <c r="N37" s="226"/>
+      <c r="O37" s="226"/>
+    </row>
+    <row r="38" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="226" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="243"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="243"/>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-    </row>
-    <row r="39" spans="4:20" ht="5.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E38" s="226"/>
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="226"/>
+      <c r="I38" s="226"/>
+      <c r="J38" s="226"/>
+      <c r="K38" s="226"/>
+      <c r="L38" s="226"/>
+      <c r="M38" s="226"/>
+      <c r="N38" s="226"/>
+      <c r="O38" s="226"/>
+    </row>
+    <row r="39" spans="4:20" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -7320,151 +7127,151 @@
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
     </row>
-    <row r="40" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="244" t="s">
+    <row r="40" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="227" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
-      <c r="M40" s="244"/>
-      <c r="N40" s="244"/>
-      <c r="O40" s="244"/>
-    </row>
-    <row r="41" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D41" s="244" t="s">
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
+      <c r="O40" s="227"/>
+    </row>
+    <row r="41" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="227" t="s">
         <v>41</v>
       </c>
-      <c r="E41" s="244"/>
-      <c r="F41" s="244"/>
-      <c r="G41" s="244"/>
-      <c r="H41" s="244"/>
-      <c r="I41" s="244"/>
-      <c r="J41" s="244"/>
-      <c r="K41" s="244"/>
-      <c r="L41" s="244"/>
-      <c r="M41" s="244"/>
-      <c r="N41" s="244"/>
-      <c r="O41" s="244"/>
-    </row>
-    <row r="42" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="244" t="s">
+      <c r="E41" s="227"/>
+      <c r="F41" s="227"/>
+      <c r="G41" s="227"/>
+      <c r="H41" s="227"/>
+      <c r="I41" s="227"/>
+      <c r="J41" s="227"/>
+      <c r="K41" s="227"/>
+      <c r="L41" s="227"/>
+      <c r="M41" s="227"/>
+      <c r="N41" s="227"/>
+      <c r="O41" s="227"/>
+    </row>
+    <row r="42" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="227" t="s">
         <v>28</v>
       </c>
-      <c r="E42" s="244"/>
-      <c r="F42" s="244"/>
-      <c r="G42" s="244"/>
-      <c r="H42" s="244"/>
-      <c r="I42" s="244"/>
-      <c r="J42" s="244"/>
-      <c r="K42" s="244"/>
-      <c r="L42" s="244"/>
-      <c r="M42" s="244"/>
-      <c r="N42" s="244"/>
-      <c r="O42" s="244"/>
-    </row>
-    <row r="43" spans="4:20" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="4:20" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="E42" s="227"/>
+      <c r="F42" s="227"/>
+      <c r="G42" s="227"/>
+      <c r="H42" s="227"/>
+      <c r="I42" s="227"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="227"/>
+      <c r="L42" s="227"/>
+      <c r="M42" s="227"/>
+      <c r="N42" s="227"/>
+      <c r="O42" s="227"/>
+    </row>
+    <row r="43" spans="4:20" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="4:20" s="32" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="D44" s="3" t="s">
         <v>38</v>
       </c>
       <c r="P44" s="33"/>
     </row>
-    <row r="45" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="1"/>
-      <c r="M45" s="245" t="s">
+      <c r="M45" s="228" t="s">
         <v>29</v>
       </c>
-      <c r="N45" s="245"/>
-      <c r="O45" s="245"/>
-    </row>
-    <row r="46" spans="4:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="4:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D47" s="240" t="s">
+      <c r="N45" s="228"/>
+      <c r="O45" s="228"/>
+    </row>
+    <row r="46" spans="4:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="4:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D47" s="223" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="240"/>
-      <c r="F47" s="240"/>
-      <c r="G47" s="240"/>
-      <c r="H47" s="240"/>
-      <c r="I47" s="240"/>
-      <c r="J47" s="240"/>
-      <c r="K47" s="240"/>
-      <c r="L47" s="240"/>
-      <c r="M47" s="240"/>
-      <c r="N47" s="240"/>
-      <c r="O47" s="240"/>
-    </row>
-    <row r="48" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D48" s="241" t="s">
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="223"/>
+      <c r="H47" s="223"/>
+      <c r="I47" s="223"/>
+      <c r="J47" s="223"/>
+      <c r="K47" s="223"/>
+      <c r="L47" s="223"/>
+      <c r="M47" s="223"/>
+      <c r="N47" s="223"/>
+      <c r="O47" s="223"/>
+    </row>
+    <row r="48" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="241"/>
-      <c r="F48" s="241"/>
-      <c r="G48" s="241"/>
-      <c r="H48" s="241"/>
-      <c r="I48" s="241"/>
-      <c r="J48" s="241"/>
-      <c r="K48" s="241"/>
-      <c r="L48" s="241"/>
-      <c r="M48" s="241"/>
-      <c r="N48" s="241"/>
-      <c r="O48" s="241"/>
-    </row>
-    <row r="49" spans="4:15" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="4:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D50" s="242" t="s">
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
+      <c r="H48" s="224"/>
+      <c r="I48" s="224"/>
+      <c r="J48" s="224"/>
+      <c r="K48" s="224"/>
+      <c r="L48" s="224"/>
+      <c r="M48" s="224"/>
+      <c r="N48" s="224"/>
+      <c r="O48" s="224"/>
+    </row>
+    <row r="49" spans="4:15" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="4:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D50" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="242"/>
-      <c r="F50" s="242"/>
-      <c r="G50" s="242"/>
-      <c r="H50" s="242"/>
-      <c r="I50" s="242"/>
-      <c r="J50" s="242"/>
-      <c r="K50" s="242"/>
-      <c r="L50" s="242"/>
-      <c r="M50" s="242"/>
-      <c r="N50" s="242"/>
-      <c r="O50" s="242"/>
+      <c r="E50" s="225"/>
+      <c r="F50" s="225"/>
+      <c r="G50" s="225"/>
+      <c r="H50" s="225"/>
+      <c r="I50" s="225"/>
+      <c r="J50" s="225"/>
+      <c r="K50" s="225"/>
+      <c r="L50" s="225"/>
+      <c r="M50" s="225"/>
+      <c r="N50" s="225"/>
+      <c r="O50" s="225"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="D29:O29"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="D21:O21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="D2:H4"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="D16:O16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="I17:O17"/>
+    <mergeCell ref="I18:O19"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="D6:O6"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D47:O47"/>
+    <mergeCell ref="D48:O48"/>
+    <mergeCell ref="D50:O50"/>
+    <mergeCell ref="D37:O37"/>
+    <mergeCell ref="D38:O38"/>
+    <mergeCell ref="D40:O40"/>
+    <mergeCell ref="D41:O41"/>
+    <mergeCell ref="D42:O42"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E9:H9"/>
     <mergeCell ref="K9:O9"/>
     <mergeCell ref="L34:M34"/>
     <mergeCell ref="L35:M35"/>
@@ -7481,36 +7288,36 @@
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="L33:M33"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="D47:O47"/>
-    <mergeCell ref="D48:O48"/>
-    <mergeCell ref="D50:O50"/>
-    <mergeCell ref="D37:O37"/>
-    <mergeCell ref="D38:O38"/>
-    <mergeCell ref="D40:O40"/>
-    <mergeCell ref="D41:O41"/>
-    <mergeCell ref="D42:O42"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="D2:H4"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="D16:O16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="I17:O17"/>
-    <mergeCell ref="I18:O19"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="D6:O6"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="D21:O21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="D29:O29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:M30"/>
   </mergeCells>
   <pageMargins left="0.43" right="0.26" top="0.45" bottom="0.46" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait"/>
@@ -7526,13 +7333,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>165100</xdr:colOff>
+                    <xdr:colOff>167640</xdr:colOff>
                     <xdr:row>29</xdr:row>
-                    <xdr:rowOff>279400</xdr:rowOff>
+                    <xdr:rowOff>281940</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>469900</xdr:colOff>
+                    <xdr:colOff>472440</xdr:colOff>
                     <xdr:row>31</xdr:row>
                     <xdr:rowOff>76200</xdr:rowOff>
                   </to>
@@ -7548,15 +7355,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>165100</xdr:colOff>
+                    <xdr:colOff>167640</xdr:colOff>
                     <xdr:row>30</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>469900</xdr:colOff>
+                    <xdr:colOff>472440</xdr:colOff>
                     <xdr:row>32</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7570,15 +7377,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>31</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>482600</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7592,15 +7399,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>32</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>482600</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>34</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7622,7 +7429,7 @@
                     <xdr:col>14</xdr:col>
                     <xdr:colOff>495300</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7636,13 +7443,13 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>165100</xdr:colOff>
+                    <xdr:colOff>167640</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>279400</xdr:rowOff>
+                    <xdr:rowOff>281940</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>469900</xdr:colOff>
+                    <xdr:colOff>472440</xdr:colOff>
                     <xdr:row>23</xdr:row>
                     <xdr:rowOff>76200</xdr:rowOff>
                   </to>
@@ -7658,15 +7465,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>165100</xdr:colOff>
+                    <xdr:colOff>167640</xdr:colOff>
                     <xdr:row>22</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>469900</xdr:colOff>
+                    <xdr:colOff>472440</xdr:colOff>
                     <xdr:row>24</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7680,15 +7487,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>23</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>482600</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>25</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7702,15 +7509,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>177800</xdr:colOff>
+                    <xdr:colOff>175260</xdr:colOff>
                     <xdr:row>24</xdr:row>
                     <xdr:rowOff>152400</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>14</xdr:col>
-                    <xdr:colOff>482600</xdr:colOff>
+                    <xdr:colOff>480060</xdr:colOff>
                     <xdr:row>26</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7732,7 +7539,7 @@
                     <xdr:col>14</xdr:col>
                     <xdr:colOff>495300</xdr:colOff>
                     <xdr:row>27</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7754,7 +7561,7 @@
                     <xdr:col>14</xdr:col>
                     <xdr:colOff>495300</xdr:colOff>
                     <xdr:row>36</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7776,7 +7583,7 @@
                     <xdr:col>14</xdr:col>
                     <xdr:colOff>495300</xdr:colOff>
                     <xdr:row>28</xdr:row>
-                    <xdr:rowOff>63500</xdr:rowOff>
+                    <xdr:rowOff>60960</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -7797,7 +7604,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -7811,7 +7618,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
